--- a/src/prevalidador/config/catalogs/catalog_nph.xlsx
+++ b/src/prevalidador/config/catalogs/catalog_nph.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\OneDrive\Escritorio\prevalidador - copia\src\prevalidador\config\catalogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2059C8-A937-4B69-B016-A04F19EAB61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A08AEA-5FD0-4B5F-9D5A-81F51BB19CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="853" firstSheet="4" activeTab="8" xr2:uid="{00B05B66-C86A-44F2-A8A3-CC89189185B5}"/>
+    <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11325" tabRatio="853" firstSheet="7" activeTab="15" xr2:uid="{00B05B66-C86A-44F2-A8A3-CC89189185B5}"/>
   </bookViews>
   <sheets>
     <sheet name="ModeloRegistral" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="911">
   <si>
     <t>NUE|Nuevo</t>
   </si>
@@ -1124,477 +1124,6 @@
   </si>
   <si>
     <t>954|Anexo.Glamping</t>
-  </si>
-  <si>
-    <t>0|IGAC_SIN_NOMBRE_00</t>
-  </si>
-  <si>
-    <t>1|Vivienda hasta 3 pisos</t>
-  </si>
-  <si>
-    <t>2|Ramadas - Cobertizos - Caneyes</t>
-  </si>
-  <si>
-    <t>3|Galpones - Gallineros</t>
-  </si>
-  <si>
-    <t>4|Establos - Pesebreras - Caballerizas</t>
-  </si>
-  <si>
-    <t>5|Cocheras - Marraneras - Porquerizas</t>
-  </si>
-  <si>
-    <t>6|Bodega Casa Bomba</t>
-  </si>
-  <si>
-    <t>7|Industrias</t>
-  </si>
-  <si>
-    <t>8|Silos</t>
-  </si>
-  <si>
-    <t>9|Piscinas</t>
-  </si>
-  <si>
-    <t>10|Tanques</t>
-  </si>
-  <si>
-    <t>11|Beneficiaderos</t>
-  </si>
-  <si>
-    <t>12|Colegios y Universidades</t>
-  </si>
-  <si>
-    <t>13|Biblioteca</t>
-  </si>
-  <si>
-    <t>14|Garajes Cubiertos</t>
-  </si>
-  <si>
-    <t>15|Depositos Lockers</t>
-  </si>
-  <si>
-    <t>16|Bodegas Comerciales - Grandes Almacenes</t>
-  </si>
-  <si>
-    <t>17|Museos</t>
-  </si>
-  <si>
-    <t>18|Secaderos</t>
-  </si>
-  <si>
-    <t>19|Clínicas - Hospitales - Centros Médicos</t>
-  </si>
-  <si>
-    <t>20|Pozos</t>
-  </si>
-  <si>
-    <t>21|Kioscos</t>
-  </si>
-  <si>
-    <t>22|Parques Diversiones</t>
-  </si>
-  <si>
-    <t>23|Albercas - Bañaderas</t>
-  </si>
-  <si>
-    <t>24|Cimientos, Estructuras, Muros y Placa Base</t>
-  </si>
-  <si>
-    <t>25|Hoteles en PH</t>
-  </si>
-  <si>
-    <t>26|Corrales</t>
-  </si>
-  <si>
-    <t>27|Casa Elbas</t>
-  </si>
-  <si>
-    <t>28|Comercio</t>
-  </si>
-  <si>
-    <t>29|Iglesia</t>
-  </si>
-  <si>
-    <t>30|Instalaciones Militares</t>
-  </si>
-  <si>
-    <t>31|Hoteles</t>
-  </si>
-  <si>
-    <t>32|Pista Aeropuerto</t>
-  </si>
-  <si>
-    <t>33|Clubes y Casinos</t>
-  </si>
-  <si>
-    <t>34|Oficinas - Consultorios</t>
-  </si>
-  <si>
-    <t>35|Apartamentos más de 4 Pisos</t>
-  </si>
-  <si>
-    <t>36|Restaurantes</t>
-  </si>
-  <si>
-    <t>37|Pensiones y Residencias</t>
-  </si>
-  <si>
-    <t>38|Puestos de Salud</t>
-  </si>
-  <si>
-    <t>39|Parqueaderos</t>
-  </si>
-  <si>
-    <t>40|Barracas</t>
-  </si>
-  <si>
-    <t>41|Teatro y Cinemas</t>
-  </si>
-  <si>
-    <t>42|Aulas de Clases</t>
-  </si>
-  <si>
-    <t>43|Coliseos</t>
-  </si>
-  <si>
-    <t>44|Casas de Culto</t>
-  </si>
-  <si>
-    <t>45|Talleres</t>
-  </si>
-  <si>
-    <t>46|Jardín Infantil en Casa</t>
-  </si>
-  <si>
-    <t>47|Torres de Enfriamiento</t>
-  </si>
-  <si>
-    <t>48|Muelles</t>
-  </si>
-  <si>
-    <t>49|Estación de Bombeo</t>
-  </si>
-  <si>
-    <t>50|Estadios, Plaza de Toros</t>
-  </si>
-  <si>
-    <t>51|Cárceles</t>
-  </si>
-  <si>
-    <t>52|Parque, Cementerios</t>
-  </si>
-  <si>
-    <t>53|Vivienda Colonial</t>
-  </si>
-  <si>
-    <t>54|Comercio Colonial</t>
-  </si>
-  <si>
-    <t>55|Oficinas - Consultorios Coloniales</t>
-  </si>
-  <si>
-    <t>58|Centros Comerciales</t>
-  </si>
-  <si>
-    <t>60|Canchas de Tenis</t>
-  </si>
-  <si>
-    <t>62|Toboganes</t>
-  </si>
-  <si>
-    <t>63|Vivienda Recreacional</t>
-  </si>
-  <si>
-    <t>70|Vivienda hasta 3 pisos en PH</t>
-  </si>
-  <si>
-    <t>71|Apartamentos 4 y más pisos en PH</t>
-  </si>
-  <si>
-    <t>72|Vivienda Recreacional en PH</t>
-  </si>
-  <si>
-    <t>73|Bodega Casa Bomba en PH</t>
-  </si>
-  <si>
-    <t>74|Bodegas Comerciales en PH</t>
-  </si>
-  <si>
-    <t>75|Comercio en PH</t>
-  </si>
-  <si>
-    <t>76|Centros Comerciales en PH</t>
-  </si>
-  <si>
-    <t>77|Oficinas Consultorios en PH</t>
-  </si>
-  <si>
-    <t>78|Parqueaderos en PH</t>
-  </si>
-  <si>
-    <t>79|Garajes en PH</t>
-  </si>
-  <si>
-    <t>80|Industrias en PH</t>
-  </si>
-  <si>
-    <t>82|Marquesinas, Patios Cubiertos</t>
-  </si>
-  <si>
-    <t>83|Lagunas de Oxidación</t>
-  </si>
-  <si>
-    <t>84|Vía Férrea</t>
-  </si>
-  <si>
-    <t>85|Carretera</t>
-  </si>
-  <si>
-    <t>86|Teatro y Cinemas en PH</t>
-  </si>
-  <si>
-    <t>87|Iglesia en PH</t>
-  </si>
-  <si>
-    <t>88|Restaurantes en PH</t>
-  </si>
-  <si>
-    <t>89|Hotel Colonial</t>
-  </si>
-  <si>
-    <t>90|Restaurante Colonial</t>
-  </si>
-  <si>
-    <t>91|Entidad Educativa Colonial - Colegio Colonial</t>
-  </si>
-  <si>
-    <t>1|EDIFICACIONES RURALES (VIVIENDA HASTA 3 PISOS)</t>
-  </si>
-  <si>
-    <t>10|INDUSTRIAS</t>
-  </si>
-  <si>
-    <t>11|IGLESIAS</t>
-  </si>
-  <si>
-    <t>12|TEATROS Y/0 AUDITORIOS</t>
-  </si>
-  <si>
-    <t>12|COLEGIOS</t>
-  </si>
-  <si>
-    <t>13|CARCELES</t>
-  </si>
-  <si>
-    <t>14|PARQUEADEROS, GARAJES, CUARTOS UTILES</t>
-  </si>
-  <si>
-    <t>15|BENEFICIADEROS</t>
-  </si>
-  <si>
-    <t>16|PORQUERIZAS</t>
-  </si>
-  <si>
-    <t>16|BODEGAS COMERCIALES</t>
-  </si>
-  <si>
-    <t>17|ESTABLOS Y PESEBRERAS</t>
-  </si>
-  <si>
-    <t>18|GALPONES Y GALLINEROS</t>
-  </si>
-  <si>
-    <t>19|TANQUES</t>
-  </si>
-  <si>
-    <t>19|HOSPITALES, CLÍNICAS</t>
-  </si>
-  <si>
-    <t>20|PISCINAS</t>
-  </si>
-  <si>
-    <t>24|ESTADIOS, PLAZAS DE TOROS,</t>
-  </si>
-  <si>
-    <t>25|CONSTRUCC DE CEMENTERIOS</t>
-  </si>
-  <si>
-    <t>25|HOTELES EN P.H</t>
-  </si>
-  <si>
-    <t>26|SILOS</t>
-  </si>
-  <si>
-    <t>27|CASA ELBAS</t>
-  </si>
-  <si>
-    <t>28|COMERCIO</t>
-  </si>
-  <si>
-    <t>28|CANCHAS DE TENIS</t>
-  </si>
-  <si>
-    <t>29|IGLESIAS</t>
-  </si>
-  <si>
-    <t>31|CLUBES Y CASINOS</t>
-  </si>
-  <si>
-    <t>32|TOBOGANES</t>
-  </si>
-  <si>
-    <t>33|CLUBES, CASINOS</t>
-  </si>
-  <si>
-    <t>34|COLISEO</t>
-  </si>
-  <si>
-    <t>35|APARTAMENTOS MÁS DE 4 PISOS</t>
-  </si>
-  <si>
-    <t>37|PATIOS ELECTRICOS</t>
-  </si>
-  <si>
-    <t>40|EDIFICACIONES AISLADAS CLASIFICACI'ON B NO VA MAS</t>
-  </si>
-  <si>
-    <t>42|AULAS DE CLASE</t>
-  </si>
-  <si>
-    <t>43|COLISEOS</t>
-  </si>
-  <si>
-    <t>44|CASAS DE CULTO</t>
-  </si>
-  <si>
-    <t>46|JARDÍN INFANTIL EN CASA</t>
-  </si>
-  <si>
-    <t>49|ESTACIONES DE BOMBEO</t>
-  </si>
-  <si>
-    <t>50|ESTADIO, PLAZAS DE TOROS</t>
-  </si>
-  <si>
-    <t>51|OFICINAS Y CONSULTORIOS EN  URBANOS</t>
-  </si>
-  <si>
-    <t>53|VIVIENDA COLONIAL</t>
-  </si>
-  <si>
-    <t>54|CONSTRUCCIONES HOTELERAS</t>
-  </si>
-  <si>
-    <t>56|APTOS EN EDIFICIOS 4 Y 5 PISOS (CARTAGENA)</t>
-  </si>
-  <si>
-    <t>58|CONSTRUCCIONES PARA DISTRIBUCION BIENES Y SERVICIOS CLASIFICACION B</t>
-  </si>
-  <si>
-    <t>6|BODEGAS</t>
-  </si>
-  <si>
-    <t>63|VIVIENDA RECREACIONAL</t>
-  </si>
-  <si>
-    <t>63|EDIFICIOS COMPLEJOS E INTEGRADOS COMERCIALES</t>
-  </si>
-  <si>
-    <t>64|EDIFICIOS DE TRANSFORMACION Y/O BODEGAJE</t>
-  </si>
-  <si>
-    <t>65|EDIFICACIONES O LOCALES LIVIANOS DE TRANSFORMACION Y/O BODEGAJE</t>
-  </si>
-  <si>
-    <t>66|TRAPICHES</t>
-  </si>
-  <si>
-    <t>67|ESCENARIOS CIVICOS INDUSTRIALES</t>
-  </si>
-  <si>
-    <t>68|CENTROS EMPRESARIALES</t>
-  </si>
-  <si>
-    <t>69|CENTROS EMPRESARIALES CLASIFICACION B NO VA MAS</t>
-  </si>
-  <si>
-    <t>70|VIVIENDA HASTA 3 PISOS EN P.H</t>
-  </si>
-  <si>
-    <t>70|PARQUEADEROS ESTRUCTURA CUBIERTA DE SERVICIO PUBLICO O PRIVADO</t>
-  </si>
-  <si>
-    <t>71|APARTAMENTOS 4 Y MAS PISOS EN P.H</t>
-  </si>
-  <si>
-    <t>71|PARQUEADEROS COMERCIALES ESTRUCTURA CUBIERTA CLASIFICACION B NO VA MAS</t>
-  </si>
-  <si>
-    <t>72|VIVIENDA RECREACIONAL EN P.H</t>
-  </si>
-  <si>
-    <t>72|PARQUEADEROS CIELO ABIERTO PUBLICOS O PRIVADOS CLASIFICACION A</t>
-  </si>
-  <si>
-    <t>73|PARQUEADEROS CIELO ABIERTO PUBLICOS O PRIVADOS CLASIFICACION B NO VA MAS</t>
-  </si>
-  <si>
-    <t>74|PARQUEADEROS CIELO ABIERTO PUBLICOS O PRIVADOS CLASIFICACION C NO VA MAS</t>
-  </si>
-  <si>
-    <t>74|BODEGAS COMERCIALES EN P.H</t>
-  </si>
-  <si>
-    <t>75|PARQUEADEROS A CIELO ABIERTO Y/O COBIERTO</t>
-  </si>
-  <si>
-    <t>75|COMERCIO EN P.H</t>
-  </si>
-  <si>
-    <t>76|CENTROS COMERCIALES EN P.H</t>
-  </si>
-  <si>
-    <t>76|ESTACIONES DE SERVICIO Y/O SERVITECAS</t>
-  </si>
-  <si>
-    <t>77|PLACAS Y/O CANCHAS POLIDEPORTIVAS</t>
-  </si>
-  <si>
-    <t>78|INFRAESTRUCTRA DE OBRA CIVIL PRIVADA Y/O SERVICIO PUBLICO</t>
-  </si>
-  <si>
-    <t>79|GARAJES EN P.H</t>
-  </si>
-  <si>
-    <t>79|ENTABLES MINEROS</t>
-  </si>
-  <si>
-    <t>80|EMPACADORAS DE BANANO</t>
-  </si>
-  <si>
-    <t>81|CUARTO FRIOS</t>
-  </si>
-  <si>
-    <t>82|COMANDOS DE POLICIA</t>
-  </si>
-  <si>
-    <t>83|MATADEROS</t>
-  </si>
-  <si>
-    <t>84|ESTACIONES DE TRANSPORTE</t>
-  </si>
-  <si>
-    <t>85|PLANTAS DE TRATAMIENTO DE AGUAS</t>
-  </si>
-  <si>
-    <t>87|IGLESIAS EN P.H</t>
-  </si>
-  <si>
-    <t>89|HOTEL COLONIAL</t>
-  </si>
-  <si>
-    <t>91|ENTIDAD EDUCATIVA COLONIAL - COLEGIO COLONIAL</t>
   </si>
   <si>
     <t>0|Sin Tipificación</t>
@@ -4075,7 +3604,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25A9F8FF-7683-453D-92CD-85EF01090DD3}">
-  <dimension ref="A1:A259"/>
+  <dimension ref="A1:A102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -4586,791 +4115,6 @@
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>346</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A216" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A217" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A218" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A219" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A220" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A221" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A222" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A223" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A224" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A225" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A227" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A228" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A230" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A231" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A235" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A237" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A238" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A240" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A242" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A243" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A244" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A245" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A246" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A247" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A248" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A250" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A251" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A252" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A253" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A254" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A255" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A257" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A258" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A259" t="s">
-        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -5385,47 +4129,47 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>504</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>505</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>506</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>507</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>508</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>509</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>510</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>511</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>512</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -5443,52 +4187,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>513</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>514</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>515</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>516</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>517</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>518</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>519</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>520</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>521</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>522</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -5503,892 +4247,892 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>523</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>524</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>525</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>526</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>527</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>528</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>529</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>530</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>531</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>532</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>533</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>534</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>535</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>536</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>537</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>538</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>539</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>540</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>541</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>542</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>543</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>544</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>545</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>546</v>
+        <v>389</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>547</v>
+        <v>390</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>548</v>
+        <v>391</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>549</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>550</v>
+        <v>393</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>551</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>552</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>553</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>554</v>
+        <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>555</v>
+        <v>398</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>556</v>
+        <v>399</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>557</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>558</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>559</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>560</v>
+        <v>403</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>561</v>
+        <v>404</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>562</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>563</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>564</v>
+        <v>407</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>565</v>
+        <v>408</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>566</v>
+        <v>409</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>567</v>
+        <v>410</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>568</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>569</v>
+        <v>412</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>570</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>571</v>
+        <v>414</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>572</v>
+        <v>415</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>573</v>
+        <v>416</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>574</v>
+        <v>417</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>575</v>
+        <v>418</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>576</v>
+        <v>419</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>577</v>
+        <v>420</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>578</v>
+        <v>421</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>579</v>
+        <v>422</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>580</v>
+        <v>423</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>581</v>
+        <v>424</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>582</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>583</v>
+        <v>426</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>584</v>
+        <v>427</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>585</v>
+        <v>428</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>586</v>
+        <v>429</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>587</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>588</v>
+        <v>431</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>589</v>
+        <v>432</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>590</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>591</v>
+        <v>434</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>592</v>
+        <v>435</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>593</v>
+        <v>436</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>594</v>
+        <v>437</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>595</v>
+        <v>438</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>596</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>597</v>
+        <v>440</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>598</v>
+        <v>441</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>599</v>
+        <v>442</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>600</v>
+        <v>443</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>601</v>
+        <v>444</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>602</v>
+        <v>445</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>603</v>
+        <v>446</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>604</v>
+        <v>447</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>605</v>
+        <v>448</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>606</v>
+        <v>449</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>607</v>
+        <v>450</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>608</v>
+        <v>451</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>609</v>
+        <v>452</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>610</v>
+        <v>453</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>611</v>
+        <v>454</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>612</v>
+        <v>455</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>613</v>
+        <v>456</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>614</v>
+        <v>457</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>615</v>
+        <v>458</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>616</v>
+        <v>459</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>617</v>
+        <v>460</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>618</v>
+        <v>461</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>619</v>
+        <v>462</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>620</v>
+        <v>463</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>621</v>
+        <v>464</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>622</v>
+        <v>465</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>623</v>
+        <v>466</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>624</v>
+        <v>467</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>625</v>
+        <v>468</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>626</v>
+        <v>469</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>627</v>
+        <v>470</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>628</v>
+        <v>471</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>629</v>
+        <v>472</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>630</v>
+        <v>473</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>631</v>
+        <v>474</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>632</v>
+        <v>475</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>633</v>
+        <v>476</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>634</v>
+        <v>477</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>635</v>
+        <v>478</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>636</v>
+        <v>479</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>637</v>
+        <v>480</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>638</v>
+        <v>481</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>639</v>
+        <v>482</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>640</v>
+        <v>483</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>641</v>
+        <v>484</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>642</v>
+        <v>485</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>643</v>
+        <v>486</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>644</v>
+        <v>487</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>645</v>
+        <v>488</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>646</v>
+        <v>489</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>647</v>
+        <v>490</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>648</v>
+        <v>491</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>649</v>
+        <v>492</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>650</v>
+        <v>493</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>651</v>
+        <v>494</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>652</v>
+        <v>495</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>653</v>
+        <v>496</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>654</v>
+        <v>497</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>655</v>
+        <v>498</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>656</v>
+        <v>499</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>657</v>
+        <v>500</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>658</v>
+        <v>501</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>659</v>
+        <v>502</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>660</v>
+        <v>503</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>661</v>
+        <v>504</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>662</v>
+        <v>505</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>663</v>
+        <v>506</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>664</v>
+        <v>507</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>665</v>
+        <v>508</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>666</v>
+        <v>509</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>667</v>
+        <v>510</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>668</v>
+        <v>511</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>669</v>
+        <v>512</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>670</v>
+        <v>513</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>671</v>
+        <v>514</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>672</v>
+        <v>515</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>673</v>
+        <v>516</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>674</v>
+        <v>517</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>675</v>
+        <v>518</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>676</v>
+        <v>519</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>677</v>
+        <v>520</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>678</v>
+        <v>521</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>679</v>
+        <v>522</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>680</v>
+        <v>523</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>681</v>
+        <v>524</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>682</v>
+        <v>525</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>683</v>
+        <v>526</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>684</v>
+        <v>527</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>685</v>
+        <v>528</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>686</v>
+        <v>529</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>687</v>
+        <v>530</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>688</v>
+        <v>531</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>689</v>
+        <v>532</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>690</v>
+        <v>533</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>691</v>
+        <v>534</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>692</v>
+        <v>535</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>693</v>
+        <v>536</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>694</v>
+        <v>537</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>695</v>
+        <v>538</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>696</v>
+        <v>539</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>697</v>
+        <v>540</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>698</v>
+        <v>541</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>699</v>
+        <v>542</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>700</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -6571,57 +5315,57 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>701</v>
+        <v>544</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>702</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>703</v>
+        <v>546</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>704</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>705</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>706</v>
+        <v>549</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>707</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>708</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>709</v>
+        <v>552</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>710</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>711</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -6636,22 +5380,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>712</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>713</v>
+        <v>556</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>714</v>
+        <v>557</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>715</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -6666,172 +5410,172 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>716</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>717</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>718</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>719</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>720</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>721</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>722</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>723</v>
+        <v>566</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>724</v>
+        <v>567</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>725</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>726</v>
+        <v>569</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>727</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>728</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>729</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>730</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>731</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>732</v>
+        <v>575</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>733</v>
+        <v>576</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>734</v>
+        <v>577</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>735</v>
+        <v>578</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>736</v>
+        <v>579</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>737</v>
+        <v>580</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>738</v>
+        <v>581</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>739</v>
+        <v>582</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>740</v>
+        <v>583</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>741</v>
+        <v>584</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>742</v>
+        <v>585</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>743</v>
+        <v>586</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>744</v>
+        <v>587</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>745</v>
+        <v>588</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>746</v>
+        <v>589</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>747</v>
+        <v>590</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>748</v>
+        <v>591</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>749</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -6846,92 +5590,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>750</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>751</v>
+        <v>594</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>752</v>
+        <v>595</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>753</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>754</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>755</v>
+        <v>598</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>756</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>757</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>758</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>759</v>
+        <v>602</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>760</v>
+        <v>603</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>761</v>
+        <v>604</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>762</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>763</v>
+        <v>606</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>764</v>
+        <v>607</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>765</v>
+        <v>608</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>766</v>
+        <v>609</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>767</v>
+        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -6946,27 +5690,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>768</v>
+        <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>769</v>
+        <v>612</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>770</v>
+        <v>613</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>771</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>772</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -6981,27 +5725,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>773</v>
+        <v>616</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>774</v>
+        <v>617</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>775</v>
+        <v>618</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>776</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>777</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -7016,27 +5760,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>778</v>
+        <v>621</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>779</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>780</v>
+        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>781</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>782</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>
@@ -7051,32 +5795,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>783</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>784</v>
+        <v>627</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>785</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>786</v>
+        <v>629</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>787</v>
+        <v>630</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>788</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -7091,22 +5835,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>789</v>
+        <v>632</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>790</v>
+        <v>633</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>791</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>792</v>
+        <v>635</v>
       </c>
     </row>
   </sheetData>
@@ -7121,52 +5865,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>793</v>
+        <v>636</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>794</v>
+        <v>637</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>795</v>
+        <v>638</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>796</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>797</v>
+        <v>640</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>798</v>
+        <v>641</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>799</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>800</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>801</v>
+        <v>644</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>802</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -8081,27 +6825,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>803</v>
+        <v>646</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>804</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>805</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>806</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>807</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -8116,37 +6860,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>808</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>809</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>810</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>811</v>
+        <v>654</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>812</v>
+        <v>655</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>813</v>
+        <v>656</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>814</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -8161,22 +6905,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>815</v>
+        <v>658</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>816</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>817</v>
+        <v>660</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>818</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -8191,22 +6935,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>819</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>820</v>
+        <v>663</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>821</v>
+        <v>664</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>822</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -8221,32 +6965,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>823</v>
+        <v>666</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>824</v>
+        <v>667</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>825</v>
+        <v>668</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>826</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>827</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>828</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>
@@ -8261,27 +7005,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>829</v>
+        <v>672</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>830</v>
+        <v>673</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>831</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>832</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>833</v>
+        <v>676</v>
       </c>
     </row>
   </sheetData>
@@ -8296,22 +7040,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>834</v>
+        <v>677</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>835</v>
+        <v>678</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>836</v>
+        <v>679</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>837</v>
+        <v>680</v>
       </c>
     </row>
   </sheetData>
@@ -8326,22 +7070,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>838</v>
+        <v>681</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>839</v>
+        <v>682</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>840</v>
+        <v>683</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>841</v>
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -8356,32 +7100,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>842</v>
+        <v>685</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>843</v>
+        <v>686</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>844</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>845</v>
+        <v>688</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>846</v>
+        <v>689</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>847</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -8396,27 +7140,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>798</v>
+        <v>641</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>799</v>
+        <v>642</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>848</v>
+        <v>691</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>801</v>
+        <v>644</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>802</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -8446,22 +7190,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>849</v>
+        <v>692</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>850</v>
+        <v>693</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>851</v>
+        <v>694</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>852</v>
+        <v>695</v>
       </c>
     </row>
   </sheetData>
@@ -8476,22 +7220,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>853</v>
+        <v>696</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>854</v>
+        <v>697</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>855</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>856</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -8506,542 +7250,542 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>857</v>
+        <v>700</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>858</v>
+        <v>701</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>859</v>
+        <v>702</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>860</v>
+        <v>703</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>861</v>
+        <v>704</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>862</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>863</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>864</v>
+        <v>707</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>865</v>
+        <v>708</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>866</v>
+        <v>709</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>867</v>
+        <v>710</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>868</v>
+        <v>711</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>869</v>
+        <v>712</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>870</v>
+        <v>713</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>871</v>
+        <v>714</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>872</v>
+        <v>715</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>873</v>
+        <v>716</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>874</v>
+        <v>717</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>875</v>
+        <v>718</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>876</v>
+        <v>719</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>877</v>
+        <v>720</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>878</v>
+        <v>721</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>879</v>
+        <v>722</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>880</v>
+        <v>723</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>881</v>
+        <v>724</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>882</v>
+        <v>725</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>883</v>
+        <v>726</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>884</v>
+        <v>727</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>885</v>
+        <v>728</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>886</v>
+        <v>729</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>887</v>
+        <v>730</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>888</v>
+        <v>731</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>889</v>
+        <v>732</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>890</v>
+        <v>733</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>891</v>
+        <v>734</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>892</v>
+        <v>735</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>893</v>
+        <v>736</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>894</v>
+        <v>737</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>895</v>
+        <v>738</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>896</v>
+        <v>739</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>897</v>
+        <v>740</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>898</v>
+        <v>741</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>899</v>
+        <v>742</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>900</v>
+        <v>743</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>901</v>
+        <v>744</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>902</v>
+        <v>745</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>903</v>
+        <v>746</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>904</v>
+        <v>747</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>905</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>906</v>
+        <v>749</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>907</v>
+        <v>750</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>908</v>
+        <v>751</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>909</v>
+        <v>752</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>910</v>
+        <v>753</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>911</v>
+        <v>754</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>912</v>
+        <v>755</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>913</v>
+        <v>756</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>914</v>
+        <v>757</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>915</v>
+        <v>758</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>916</v>
+        <v>759</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>917</v>
+        <v>760</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>918</v>
+        <v>761</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>919</v>
+        <v>762</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>920</v>
+        <v>763</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>921</v>
+        <v>764</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>922</v>
+        <v>765</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>923</v>
+        <v>766</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>924</v>
+        <v>767</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>925</v>
+        <v>768</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>926</v>
+        <v>769</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>927</v>
+        <v>770</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>928</v>
+        <v>771</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>929</v>
+        <v>772</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>930</v>
+        <v>773</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>931</v>
+        <v>774</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>932</v>
+        <v>775</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>933</v>
+        <v>776</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>934</v>
+        <v>777</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>935</v>
+        <v>778</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>936</v>
+        <v>779</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>937</v>
+        <v>780</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>938</v>
+        <v>781</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>939</v>
+        <v>782</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>940</v>
+        <v>783</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>941</v>
+        <v>784</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>942</v>
+        <v>785</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>943</v>
+        <v>786</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>944</v>
+        <v>787</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>945</v>
+        <v>788</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>946</v>
+        <v>789</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>947</v>
+        <v>790</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>948</v>
+        <v>791</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>949</v>
+        <v>792</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>950</v>
+        <v>793</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>951</v>
+        <v>794</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>952</v>
+        <v>795</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>953</v>
+        <v>796</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>954</v>
+        <v>797</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>955</v>
+        <v>798</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>956</v>
+        <v>799</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>957</v>
+        <v>800</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>958</v>
+        <v>801</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>959</v>
+        <v>802</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>960</v>
+        <v>803</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>961</v>
+        <v>804</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>962</v>
+        <v>805</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>963</v>
+        <v>806</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>964</v>
+        <v>807</v>
       </c>
     </row>
   </sheetData>
@@ -9059,47 +7803,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1058</v>
+        <v>901</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1059</v>
+        <v>902</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1060</v>
+        <v>903</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1061</v>
+        <v>904</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1062</v>
+        <v>905</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1063</v>
+        <v>906</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1064</v>
+        <v>907</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1065</v>
+        <v>908</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1066</v>
+        <v>909</v>
       </c>
     </row>
   </sheetData>
@@ -9114,7 +7858,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>965</v>
+        <v>808</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -9144,7 +7888,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>966</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -9162,32 +7906,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>967</v>
+        <v>810</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>968</v>
+        <v>811</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>969</v>
+        <v>812</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>970</v>
+        <v>813</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>971</v>
+        <v>814</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>972</v>
+        <v>815</v>
       </c>
     </row>
   </sheetData>
@@ -9202,117 +7946,117 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>973</v>
+        <v>816</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>974</v>
+        <v>817</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>975</v>
+        <v>818</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>976</v>
+        <v>819</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>977</v>
+        <v>820</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>978</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>979</v>
+        <v>822</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>980</v>
+        <v>823</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>981</v>
+        <v>824</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>982</v>
+        <v>825</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>983</v>
+        <v>826</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>984</v>
+        <v>827</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>985</v>
+        <v>828</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>986</v>
+        <v>829</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>987</v>
+        <v>830</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>988</v>
+        <v>831</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>989</v>
+        <v>832</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>990</v>
+        <v>833</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>991</v>
+        <v>834</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>992</v>
+        <v>835</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>993</v>
+        <v>836</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>994</v>
+        <v>837</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>995</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -9327,262 +8071,262 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>996</v>
+        <v>839</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>997</v>
+        <v>840</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>998</v>
+        <v>841</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>999</v>
+        <v>842</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1000</v>
+        <v>843</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1001</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1002</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1003</v>
+        <v>846</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1004</v>
+        <v>847</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1005</v>
+        <v>848</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1006</v>
+        <v>849</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1007</v>
+        <v>850</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1008</v>
+        <v>851</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1009</v>
+        <v>852</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1010</v>
+        <v>853</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1011</v>
+        <v>854</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1012</v>
+        <v>855</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1013</v>
+        <v>856</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1014</v>
+        <v>857</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1015</v>
+        <v>858</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1016</v>
+        <v>859</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1017</v>
+        <v>860</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1018</v>
+        <v>861</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1019</v>
+        <v>862</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1020</v>
+        <v>863</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1021</v>
+        <v>864</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1022</v>
+        <v>865</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1023</v>
+        <v>866</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1024</v>
+        <v>867</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1025</v>
+        <v>868</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1026</v>
+        <v>869</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1027</v>
+        <v>870</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1028</v>
+        <v>871</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1029</v>
+        <v>872</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1030</v>
+        <v>873</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1031</v>
+        <v>874</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1032</v>
+        <v>875</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1033</v>
+        <v>876</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1034</v>
+        <v>877</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1035</v>
+        <v>878</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1036</v>
+        <v>879</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1037</v>
+        <v>880</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1038</v>
+        <v>881</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1039</v>
+        <v>882</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1040</v>
+        <v>883</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1041</v>
+        <v>884</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1042</v>
+        <v>885</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1043</v>
+        <v>886</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1044</v>
+        <v>887</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1045</v>
+        <v>888</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1046</v>
+        <v>889</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1047</v>
+        <v>890</v>
       </c>
     </row>
   </sheetData>
@@ -9597,52 +8341,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1048</v>
+        <v>891</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1049</v>
+        <v>892</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1050</v>
+        <v>893</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1051</v>
+        <v>894</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1052</v>
+        <v>895</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1053</v>
+        <v>896</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1054</v>
+        <v>897</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1055</v>
+        <v>898</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1056</v>
+        <v>899</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1057</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -9804,7 +8548,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H12" t="s">
-        <v>1067</v>
+        <v>910</v>
       </c>
     </row>
     <row r="20" spans="9:9" x14ac:dyDescent="0.3">

--- a/src/prevalidador/config/catalogs/catalog_nph.xlsx
+++ b/src/prevalidador/config/catalogs/catalog_nph.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manue\OneDrive\Escritorio\prevalidador - copia\src\prevalidador\config\catalogs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\validador\PREVALIDADOR\src\prevalidador\config\catalogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A08AEA-5FD0-4B5F-9D5A-81F51BB19CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03897426-DD80-4958-99F0-5614C87B6BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11325" tabRatio="853" firstSheet="7" activeTab="15" xr2:uid="{00B05B66-C86A-44F2-A8A3-CC89189185B5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="853" firstSheet="27" activeTab="30" xr2:uid="{00B05B66-C86A-44F2-A8A3-CC89189185B5}"/>
   </bookViews>
   <sheets>
     <sheet name="ModeloRegistral" sheetId="1" r:id="rId1"/>
-    <sheet name="DestinoEconomico" sheetId="2" r:id="rId2"/>
-    <sheet name="TipoMutacion" sheetId="3" r:id="rId3"/>
-    <sheet name="CaracteristicaPredio" sheetId="4" r:id="rId4"/>
-    <sheet name="Sino" sheetId="5" r:id="rId5"/>
-    <sheet name="PredioLcTipo" sheetId="6" r:id="rId6"/>
-    <sheet name="Tipo_Direccion" sheetId="7" r:id="rId7"/>
-    <sheet name="ModoAdquisicion" sheetId="8" r:id="rId8"/>
+    <sheet name="TipoMutacion" sheetId="3" r:id="rId2"/>
+    <sheet name="DestinoEconomico" sheetId="2" r:id="rId3"/>
+    <sheet name="ModoAdquisicion" sheetId="8" r:id="rId4"/>
+    <sheet name="PredioLcTipo" sheetId="6" r:id="rId5"/>
+    <sheet name="CaracteristicaPredio" sheetId="4" r:id="rId6"/>
+    <sheet name="Sino" sheetId="5" r:id="rId7"/>
+    <sheet name="Tipo_Direccion" sheetId="7" r:id="rId8"/>
     <sheet name="TipoDocumento" sheetId="9" r:id="rId9"/>
     <sheet name="TipoZonas" sheetId="11" r:id="rId10"/>
     <sheet name="TipoConstruccion" sheetId="12" r:id="rId11"/>
@@ -37,30 +37,13 @@
     <sheet name="Departamento" sheetId="24" r:id="rId22"/>
     <sheet name="Entidad" sheetId="25" r:id="rId23"/>
     <sheet name="ConstrGeneral" sheetId="26" r:id="rId24"/>
-    <sheet name="DM_ARMAZON" sheetId="27" r:id="rId25"/>
-    <sheet name="DM_MUROS" sheetId="28" r:id="rId26"/>
-    <sheet name="DM_CUBIERTA" sheetId="29" r:id="rId27"/>
-    <sheet name="DM_CONSERV" sheetId="30" r:id="rId28"/>
-    <sheet name="DM_FACHADAS" sheetId="31" r:id="rId29"/>
-    <sheet name="DM_CUBRIMIENTOS_MUROS" sheetId="32" r:id="rId30"/>
-    <sheet name="DM_PISOS" sheetId="33" r:id="rId31"/>
-    <sheet name="DM_CONSERV_ACABADOS_PPALES" sheetId="34" r:id="rId32"/>
-    <sheet name="DM_TAMAÑO_BAÑO" sheetId="35" r:id="rId33"/>
-    <sheet name="DM_ENCHAPES_BAÑO" sheetId="36" r:id="rId34"/>
-    <sheet name="DM_MOBILIARIO_BAÑO" sheetId="37" r:id="rId35"/>
-    <sheet name="DM_CONSERV_BAÑO" sheetId="38" r:id="rId36"/>
-    <sheet name="DM_TAMAÑO" sheetId="39" r:id="rId37"/>
-    <sheet name="DM_ENCHAPES" sheetId="40" r:id="rId38"/>
-    <sheet name="DM_MOBILIARIO" sheetId="41" r:id="rId39"/>
-    <sheet name="DM_CONSERV_COCINA" sheetId="42" r:id="rId40"/>
-    <sheet name="DM_COMPLEMENTO_INDUSTRIAL" sheetId="43" r:id="rId41"/>
-    <sheet name="calificacionNoConvencional" sheetId="44" r:id="rId42"/>
-    <sheet name="ConservacionTipologia" sheetId="52" r:id="rId43"/>
-    <sheet name="ILC_PREDIOTIPO" sheetId="45" r:id="rId44"/>
-    <sheet name="ILC_AutorreconocimientoEtnicoTi" sheetId="46" r:id="rId45"/>
-    <sheet name="ILC_EstructuraNovedadNumeroPred" sheetId="47" r:id="rId46"/>
-    <sheet name="CUC_TipologiaTipo" sheetId="48" r:id="rId47"/>
-    <sheet name="Clase_Via_Principal" sheetId="49" r:id="rId48"/>
+    <sheet name="calificacionNoConvencional" sheetId="44" r:id="rId25"/>
+    <sheet name="ConservacionTipologia" sheetId="52" r:id="rId26"/>
+    <sheet name="ILC_PREDIOTIPO" sheetId="45" r:id="rId27"/>
+    <sheet name="ILC_AutorreconocimientoEtnicoTi" sheetId="46" r:id="rId28"/>
+    <sheet name="ILC_EstructuraNovedadNumeroPred" sheetId="47" r:id="rId29"/>
+    <sheet name="CUC_TipologiaTipo" sheetId="48" r:id="rId30"/>
+    <sheet name="Clase_Via_Principal" sheetId="49" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -83,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="826">
   <si>
     <t>NUE|Nuevo</t>
   </si>
@@ -796,9 +779,6 @@
     <t>T</t>
   </si>
   <si>
-    <t>Convencional(Tradicional)</t>
-  </si>
-  <si>
     <t>Convencional(Tipologia)</t>
   </si>
   <si>
@@ -1933,258 +1913,6 @@
     <t>005|GAS</t>
   </si>
   <si>
-    <t>111|MADERA, TAPIA</t>
-  </si>
-  <si>
-    <t>112|PREFABRICADO</t>
-  </si>
-  <si>
-    <t>113|LADRILLO,BLOQUE,MADERA INMUNIZADA</t>
-  </si>
-  <si>
-    <t>114|CONCRETO HASTA TRES PISOS</t>
-  </si>
-  <si>
-    <t>115|CONCRETO CUATRO O MAS PISOS</t>
-  </si>
-  <si>
-    <t>121|MATERIALES DE DESECHOS,ESTERILLA</t>
-  </si>
-  <si>
-    <t>122|BAHAREQUE,ADOBE, TAPIA</t>
-  </si>
-  <si>
-    <t>123|MADERA</t>
-  </si>
-  <si>
-    <t>124|CONCRETO PREFABRICADO</t>
-  </si>
-  <si>
-    <t>125|BLOQUE,LADRILLO,MADERA FINA</t>
-  </si>
-  <si>
-    <t>131|MATERIALES DE DESECHO</t>
-  </si>
-  <si>
-    <t>132|ZINC,TEJA DE BARRO</t>
-  </si>
-  <si>
-    <t>133|ENTREPISO</t>
-  </si>
-  <si>
-    <t>134|ETERNIT O TEJA DE BARRO</t>
-  </si>
-  <si>
-    <t>135|AZOTEA, ALUMINIO,PLACAS CON ETERNIT</t>
-  </si>
-  <si>
-    <t>136|PLACA IMPERMEABILI, CUBIERTA DE LUJO</t>
-  </si>
-  <si>
-    <t>141|MALO</t>
-  </si>
-  <si>
-    <t>142|REGULAR</t>
-  </si>
-  <si>
-    <t>143|BUENO</t>
-  </si>
-  <si>
-    <t>144|EXCELENTE</t>
-  </si>
-  <si>
-    <t>211|POBRE</t>
-  </si>
-  <si>
-    <t>212|SENCILLA</t>
-  </si>
-  <si>
-    <t>213|REGULAR</t>
-  </si>
-  <si>
-    <t>214|BUENA</t>
-  </si>
-  <si>
-    <t>215|LUJOSA</t>
-  </si>
-  <si>
-    <t>431|POBRE</t>
-  </si>
-  <si>
-    <t>432|SENCILLO</t>
-  </si>
-  <si>
-    <t>433|REGULA</t>
-  </si>
-  <si>
-    <t>434|BUENO</t>
-  </si>
-  <si>
-    <t>435|LUJOSO</t>
-  </si>
-  <si>
-    <t>221|SIN CUBRIMIENTO</t>
-  </si>
-  <si>
-    <t>222|PAÑETE, PAPEL, COMÚN, LADRILLO PRENSADO</t>
-  </si>
-  <si>
-    <t>223|ESTUCO, CERÁMICA, PAPEL FINO</t>
-  </si>
-  <si>
-    <t>224|MADERA, PIEDRA ORNAMENT. LADRILLO FINO</t>
-  </si>
-  <si>
-    <t>225|MÁRMOL, LUJOSOS, OTROS</t>
-  </si>
-  <si>
-    <t>231|TIERRA PISADA</t>
-  </si>
-  <si>
-    <t>232|CEMENTO, MADERA BURDA</t>
-  </si>
-  <si>
-    <t>233|BALDOSA COMÚN DE CEMENTO, TABLÓN LADR</t>
-  </si>
-  <si>
-    <t>234|LISTÓN MACHIMEMBRADO</t>
-  </si>
-  <si>
-    <t>235|TABLETA, CAUCHO, ACRÍLICO, GRANITO, BALDOSAS FINA, CERÁMICA</t>
-  </si>
-  <si>
-    <t>236|PARQUET, ALFONFRA, RETAL DE MÁRMOL</t>
-  </si>
-  <si>
-    <t>237|MÁRMOL, OTROS LUJOSOS</t>
-  </si>
-  <si>
-    <t>241|MALO</t>
-  </si>
-  <si>
-    <t>242|REGULAR</t>
-  </si>
-  <si>
-    <t>243|BUENO</t>
-  </si>
-  <si>
-    <t>244|EXCELENTE</t>
-  </si>
-  <si>
-    <t>311|SIN BAÑO</t>
-  </si>
-  <si>
-    <t>312|PEQUEÑO</t>
-  </si>
-  <si>
-    <t>313|MEDIANO</t>
-  </si>
-  <si>
-    <t>314|GRANDE</t>
-  </si>
-  <si>
-    <t>321|SIN CUBRIMIENTO</t>
-  </si>
-  <si>
-    <t>322|PAÑETE, BALDOSA COMÚN DE CEMENTO</t>
-  </si>
-  <si>
-    <t>323|BALDOSÍN, PAPEL COMÚN</t>
-  </si>
-  <si>
-    <t>324|CRISTANAC. GRANITO, PAPEL FINO</t>
-  </si>
-  <si>
-    <t>325|CERÁMICA</t>
-  </si>
-  <si>
-    <t>326|MÁRMOL, ENCHAPE LUJOSO</t>
-  </si>
-  <si>
-    <t>331|POBRE</t>
-  </si>
-  <si>
-    <t>332|SENCILLO</t>
-  </si>
-  <si>
-    <t>333|REGULAR</t>
-  </si>
-  <si>
-    <t>334|BUENO</t>
-  </si>
-  <si>
-    <t>335|LUJOSO</t>
-  </si>
-  <si>
-    <t>341|MALO</t>
-  </si>
-  <si>
-    <t>342|REGULAR</t>
-  </si>
-  <si>
-    <t>343|BUENO</t>
-  </si>
-  <si>
-    <t>344|EXCELENTE</t>
-  </si>
-  <si>
-    <t>411|SIN COCINA</t>
-  </si>
-  <si>
-    <t>412|PEQUEÑA</t>
-  </si>
-  <si>
-    <t>413|MEDIANA</t>
-  </si>
-  <si>
-    <t>414|GRANDE</t>
-  </si>
-  <si>
-    <t>421|SIN CUBRIMIENTO</t>
-  </si>
-  <si>
-    <t>422|PAÑETE, BALDOSA COMÚN DE CEMENTO</t>
-  </si>
-  <si>
-    <t>423|BALDOSÍN, PAPEL COMÚN</t>
-  </si>
-  <si>
-    <t>424|CRISTANAC. GRANITO, PAPEL FINO</t>
-  </si>
-  <si>
-    <t>425|CERÁMICA</t>
-  </si>
-  <si>
-    <t>426|MÁRMOL, ENCHAPE LUJOSO</t>
-  </si>
-  <si>
-    <t>433|REGULAR</t>
-  </si>
-  <si>
-    <t>441|MALO</t>
-  </si>
-  <si>
-    <t>442|REGULAR</t>
-  </si>
-  <si>
-    <t>443|BUENO</t>
-  </si>
-  <si>
-    <t>444|EXCELENTE</t>
-  </si>
-  <si>
-    <t>511|MADERA RÚSTICA</t>
-  </si>
-  <si>
-    <t>512|METÁLICA O DE MADERA LIVIANA</t>
-  </si>
-  <si>
-    <t>513|METÁLICA O DE MADERA MEDIANA</t>
-  </si>
-  <si>
-    <t>514|METÁLICA PESADA</t>
-  </si>
-  <si>
     <t>Ramadas_Cobertizos_Caneyes.Sencilla_Tipo_40</t>
   </si>
   <si>
@@ -2509,12 +2237,6 @@
     <t>Estructuras_Especiales.Plus_Tipo_60</t>
   </si>
   <si>
-    <t>Predio.Publico.Baldio.Reserva_Indigena</t>
-  </si>
-  <si>
-    <t>Predio.Privado.Colectivo</t>
-  </si>
-  <si>
     <t>Etnico.Indigena</t>
   </si>
   <si>
@@ -2816,6 +2538,12 @@
   </si>
   <si>
     <t xml:space="preserve"> v </t>
+  </si>
+  <si>
+    <t>10|CEDULA DE CIUDADANIA</t>
+  </si>
+  <si>
+    <t>002|ALCANTARIL</t>
   </si>
 </sst>
 </file>
@@ -3196,24 +2924,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D611201B-A3F1-4750-B283-7AD44C62C3A0}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3224,11 +2952,11 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACFD96F7-AD64-4FD9-AC25-258180334A03}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3239,26 +2967,26 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49A8758E-773F-400D-AE66-0C847AE465F5}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>236</v>
       </c>
     </row>
@@ -3269,22 +2997,17 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12220C3E-3D5B-429C-8CE0-C3ED09B6DEB7}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>238</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3294,22 +3017,22 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB789A7-37D2-47C3-9DA3-2700164D7D6F}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>241</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3319,17 +3042,17 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E7EAB1-3D14-49B1-B147-7CBA3B0C56C0}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>243</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3339,261 +3062,261 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18D51441-442E-4B29-9B5C-F0A3A3D19EBC}">
-  <dimension ref="A1:A51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>1980</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>1981</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>1982</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>1983</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>1984</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>1985</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>1986</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>1987</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>1988</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>1989</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>1990</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>1991</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>1992</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>1993</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>1994</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>1995</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>1996</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>1997</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>1998</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>1999</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>2000</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>2001</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>2002</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>2003</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>2004</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>2005</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28">
         <v>2006</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>2007</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>2008</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31">
         <v>2009</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32">
         <v>2010</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33">
         <v>2011</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34">
         <v>2012</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35">
         <v>2013</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>2014</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37">
         <v>2015</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38">
         <v>2016</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39">
         <v>2017</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40">
         <v>2018</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41">
         <v>2019</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42">
         <v>2020</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43">
         <v>2021</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44">
         <v>2022</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45">
         <v>2023</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46">
         <v>2024</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47">
         <v>2025</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48">
         <v>2026</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49">
         <v>2027</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50">
         <v>2028</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51">
         <v>2029</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52">
         <v>2030</v>
       </c>
     </row>
@@ -3604,517 +3327,517 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25A9F8FF-7683-453D-92CD-85EF01090DD3}">
-  <dimension ref="A1:A102"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -4124,56 +3847,56 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD6B7D0-015E-456C-9C5B-1D41368A89A2}">
-  <dimension ref="A1:O10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:O11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O10" s="1"/>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4182,57 +3905,57 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F68B6281-DA18-4EE6-8006-C635AA1A809B}">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>364</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -4242,897 +3965,897 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D10CDFB-4308-4BA6-98CC-76D0656A85E4}">
-  <dimension ref="A1:A178"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A179"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
         <v>542</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -5141,166 +4864,898 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC6F7DF-038C-486F-AF1B-AF5187CFBDE4}">
-  <dimension ref="A1:A31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="46.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{000574A7-565F-4262-80DD-1440A68438A7}">
+  <dimension ref="A2:A179"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -5310,62 +5765,62 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A90DC2-4B52-404D-A950-2D525194548F}">
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>553</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -5375,27 +5830,27 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FA91B8-3319-46D2-8BE4-1B7176BD7F55}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>557</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -5405,177 +5860,177 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABA972B8-48CA-4786-A081-5027340C336F}">
-  <dimension ref="A1:A34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>591</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -5585,97 +6040,97 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB8955B-C1AA-455B-8878-5D6A6A1F2551}">
-  <dimension ref="A1:A18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>609</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -5685,32 +6140,37 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C3B565-7556-4EA7-A8EB-6AAD85CA7BCE}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>615</v>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>825</v>
       </c>
     </row>
   </sheetData>
@@ -5719,33 +6179,548 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D5812D-81D2-4A68-90E8-50BA43B72D40}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA3D6612-459D-4A1D-929E-710FE437AC35}">
+  <dimension ref="A2:A109"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>620</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -5754,33 +6729,56 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79DC8D7-029E-479B-8F0C-EB5C07FE84FE}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5A6036A-73CB-4F19-A1A4-09C16D8EA1F6}">
+  <dimension ref="A2:A10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.6328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>625</v>
+        <v>817</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>822</v>
       </c>
     </row>
   </sheetData>
@@ -5789,38 +6787,33 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7733A2E-3AE8-44CA-97F9-3CA217DD4552}">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D36C6C-3447-4818-A877-2CEC2B23361E}">
+  <dimension ref="A3:A7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>631</v>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -5829,28 +6822,41 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95C7DFFE-3F64-4BBF-8D68-242080CA165E}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907668B6-96BE-4350-8A8F-EAE92288B522}">
+  <dimension ref="A2:A7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>635</v>
+        <v>725</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -5859,58 +6865,123 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A505F4EE-3C7F-468F-A3C5-1271DA8EC41F}">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9C5431-5CAE-4FFC-93EF-7BFBF5592CC8}">
+  <dimension ref="A2:A24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>645</v>
+        <v>737</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>751</v>
       </c>
     </row>
   </sheetData>
@@ -5919,898 +6990,256 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{000574A7-565F-4262-80DD-1440A68438A7}">
-  <dimension ref="A1:A178"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC6F7DF-038C-486F-AF1B-AF5187CFBDE4}">
+  <dimension ref="A1:A50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -6819,33 +7248,268 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B76F076-4BB7-4EA0-8035-9A800F248AB4}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939D55B9-1970-4B08-8099-E5B94A894850}">
+  <dimension ref="A1:A53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>650</v>
+        <v>756</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -6854,313 +7518,58 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5457B1BE-20BC-4643-A306-A46365389F6E}">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92AF1725-D5F6-44AE-9A9E-22350D76E013}">
+  <dimension ref="A2:A11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>657</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68746FB-BCEF-4B8A-BBE8-F323711608ED}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>661</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8724A281-F3BC-4828-BF34-AAB64CC2680B}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>665</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494B2F72-64D8-49FB-A00F-D26CD8D73149}">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>671</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F42CB75F-4477-428B-A9DD-FDA4AFD44BE8}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>676</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716F977C-5B55-48EA-99C7-DABF44187BB8}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>680</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F0F450-FBB4-46CA-9301-89E19D647F75}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>684</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8311E45E-BCEF-4F88-B6CD-EE88BFEC0501}">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>690</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9168FF-BC4C-4E39-9612-3301548319E0}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>645</v>
+        <v>809</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -7169,1224 +7578,23 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1760D413-EF4B-433B-A6B6-AE350A274733}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0637552-F5E9-49D8-96D9-09225FCC5DB9}">
+  <dimension ref="A2:A4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43339FB0-0902-4306-B6E8-385A7AB15B4A}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>695</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F94F9D5-FC3D-4C99-935E-22DDE3E8938A}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>699</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA3D6612-459D-4A1D-929E-710FE437AC35}">
-  <dimension ref="A1:A108"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>807</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5A6036A-73CB-4F19-A1A4-09C16D8EA1F6}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>909</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D36C6C-3447-4818-A877-2CEC2B23361E}">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>809</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907668B6-96BE-4350-8A8F-EAE92288B522}">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="27.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>815</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9C5431-5CAE-4FFC-93EF-7BFBF5592CC8}">
-  <dimension ref="A1:A23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>838</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939D55B9-1970-4B08-8099-E5B94A894850}">
-  <dimension ref="A1:A52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>890</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92AF1725-D5F6-44AE-9A9E-22350D76E013}">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>900</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -8395,22 +7603,37 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C40E661-7D94-4CD0-87CE-81A31FD643FA}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3AF237-F56D-48D5-AEB5-B5DF70379341}">
+  <dimension ref="A2:G23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B13" s="1"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8418,37 +7641,14 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3AF237-F56D-48D5-AEB5-B5DF70379341}">
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1760D413-EF4B-433B-A6B6-AE350A274733}">
+  <dimension ref="A2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G22" s="1"/>
+        <v>212</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8456,19 +7656,22 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC3D87EB-D554-44C2-B049-8CCC1C087BA6}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C40E661-7D94-4CD0-87CE-81A31FD643FA}">
+  <dimension ref="A2:B14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>221</v>
-      </c>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8476,23 +7679,18 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0637552-F5E9-49D8-96D9-09225FCC5DB9}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC3D87EB-D554-44C2-B049-8CCC1C087BA6}">
+  <dimension ref="A2:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -8502,57 +7700,62 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C592118-6E99-42E3-9AC1-F4958593A910}">
-  <dimension ref="A1:I20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:I21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C9" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H12" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="20" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I20" s="1"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C10" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H13" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="21" spans="9:9" x14ac:dyDescent="0.35">
+      <c r="I21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
